--- a/02_加值成品/九下/九下4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-2 海洋與海水運動　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下4-2 海洋與海水運動　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>風吹海面形成的是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>潮汐</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>海流</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>波浪</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>起伏</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>大範圍海水定向流動是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>黑潮</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>海流</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>原地起伏</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>流動</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>海面週期性漲落是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>潮汐</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>原地起伏</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>漲退</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>潮汐主要受什麼引力影響？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>熱量與海水</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>滿潮</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>月球</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>引力</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>臺灣附近著名的暖流是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>黑潮</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>波浪</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>潮汐</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>海流</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>風越強波浪？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>有調節作用</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>暖流</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>波浪</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>風力</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>海水漲到最高稱？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>暖流</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>滿潮</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>帶來養分聚魚</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>漲潮</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>波浪傳遞的是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>海流</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>滿潮</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>兩次</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>非水團</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>海水大範圍的定向流動稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>海流</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>潮汐</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>海流</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>海面規律的漲落現象稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>暖流</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>波浪</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>潮汐</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>潮汐</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-2 海洋與海水運動　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下4-2 海洋與海水運動　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>海流對沿岸氣候？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>原地起伏</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>暖流</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>有調節作用</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>潮汐一天多數地方有幾次？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>暖流</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>原地起伏</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>兩次</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>漲退</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>黑潮是暖流還冷流？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>暖流</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>原地起伏</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>滿潮</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>潮汐</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>溫暖</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>波浪中水的運動主要是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>原地起伏</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>滿潮</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>乾潮</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>潮汐</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>傳能</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>潮汐與月球位置關係？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>隨月球引力變化</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>水主要原地上下起伏傳遞能量</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>把低緯熱量帶往高緯調節氣候</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>週期性乾濕造就多樣棲地</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>引力</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>海流影響漁業因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>海流</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>滿潮</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>帶來養分聚魚</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>漁場</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>海水最低稱？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>帶來養分聚魚</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>熱量與海水</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>乾潮</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>滿潮</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>退潮</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>海流能長距離運送？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>潮汐</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>海流</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>熱量與海水</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>潮汐主要受哪個天體引力影響？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>海流</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>月球</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>暖流</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>黑潮</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>引力</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>臺灣東側著名的暖流是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>黑潮</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>滿潮</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>有調節作用</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>海流</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-2 海洋與海水運動　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下4-2 海洋與海水運動　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何說波浪傳遞能量而非搬運海水？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>地球自轉與月球引力共同作用</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>把低緯熱量帶往高緯調節氣候</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>月球引力使朝月側與背側海面隆起形成漲潮</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>水主要原地上下起伏傳遞能量</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>本質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>潮汐如何受月球引力造成漲退？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>月球引力使朝月側與背側海面隆起形成漲潮</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>把低緯熱量帶往高緯調節氣候</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>地球自轉與月球引力共同作用</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>隨月球引力變化</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>引力</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>黑潮暖流如何影響臺灣氣候與漁業？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>波浪風、海流定向流動、潮汐月球引力</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>帶來溫暖海水調節氣候並形成漁場</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>水主要原地上下起伏傳遞能量</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>週期性乾濕造就多樣棲地</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>海流</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>比較波浪海流潮汐三者主要成因？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>水主要原地上下起伏傳遞能量</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>月球引力使朝月側與背側海面隆起形成漲潮</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>波浪風、海流定向流動、潮汐月球引力</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>週期性乾濕造就多樣棲地</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>潮間帶生態豐富與潮汐關係？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>週期性乾濕造就多樣棲地</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>侵蝕與堆積改變海岸地形</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>地球自轉與月球引力共同作用</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>波浪風、海流定向流動、潮汐月球引力</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>生態</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>海流對全球熱量分配的意義？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>週期性乾濕造就多樣棲地</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>帶來溫暖海水調節氣候並形成漁場</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>月球引力使朝月側與背側海面隆起形成漲潮</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>把低緯熱量帶往高緯調節氣候</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>全球</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何多數海岸一天兩次滿潮？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>帶來溫暖海水調節氣候並形成漁場</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>地球自轉與月球引力共同作用</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>水主要原地上下起伏傳遞能量</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>週期性乾濕造就多樣棲地</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>週期</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>波浪長期作用如何塑造海岸？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>運送熱量調節氣候</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>侵蝕與堆積改變海岸地形</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>水主要原地上下起伏傳遞能量</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>地球自轉與月球引力共同作用</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>塑形</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>波浪中海水主要如何運動？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>把低緯熱量帶往高緯調節氣候</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>運送熱量調節氣候</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>地球自轉與月球引力共同作用</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>原地起伏傳遞能量</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>原地</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>海流對全球氣候的作用？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>波浪風、海流定向流動、潮汐月球引力</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>隨月球引力變化</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>運送熱量調節氣候</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>月球引力使朝月側與背側海面隆起形成漲潮</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>起伏</t>
+          <t>起伏：風吹過海面時會帶動水面上下起伏，形成一波波的波浪</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>流動</t>
+          <t>流動：像河流一樣朝固定方向流動的大範圍海水，稱為海流</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>漲退</t>
+          <t>漲退：海面會依照固定週期規律地升高又降低，這種現象叫潮汐</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>引力</t>
+          <t>引力：潮汐主要是因為月球對地球海水的引力拉扯所造成的</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>海流</t>
+          <t>海流：黑潮是流經臺灣附近、水溫較高的一條著名暖流</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>風力</t>
+          <t>風力：吹拂海面的風力越強，掀起的波浪也就越高越大</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>漲潮</t>
+          <t>漲潮：海面在漲潮過程中升到最高的那一刻，稱為滿潮</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>非水團</t>
+          <t>非水團：波浪傳遞出去的其實是能量，海水本身大致停留在原地上下起伏</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>海流</t>
+          <t>海流：海洋中海水沿著一定方向長期、大規模流動的現象稱為海流</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>潮汐</t>
+          <t>潮汐：海面因為受到天體引力影響而規律上升下降的現象稱為潮汐</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>影響：海流會把不同溫度的海水帶到沿岸，對當地的氣候有調節冷暖的作用</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>漲退</t>
+          <t>漲退：地球上大部分地區一天大約會經歷兩次漲潮和兩次退潮</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>溫暖</t>
+          <t>溫暖：黑潮帶著溫度較高的海水流動，屬於暖流的一種</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>傳能</t>
+          <t>傳能：波浪通過時，海水粒子主要是在原地做上下起伏的圓周運動，並沒有跟著往前移動</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>引力</t>
+          <t>引力：月球在天空中位置的變化會影響引力方向，使各地潮汐漲退的時間跟著改變</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>漁場</t>
+          <t>漁場：海流流動時會帶來豐富的營養鹽，吸引魚群聚集，形成良好的漁場</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>退潮</t>
+          <t>退潮：海面在退潮過程中降到最低的那一刻，稱為乾潮</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：海流能把大量的熱量和海水從一個地區帶到很遠的另一個地區，幫助調節全球氣候</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>引力</t>
+          <t>引力：月球離地球最近,對海水的引力影響最大,是造成潮汐現象的主要原因</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>海流</t>
+          <t>海流：黑潮是流經臺灣東側的一股強勁暖流,水溫較高、顏色深藍,因此得名</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>本質</t>
+          <t>本質：波浪經過時，海水粒子只是在原地做上下圓周運動，並沒有隨波浪往前移動，真正往前傳遞的是能量</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>引力</t>
+          <t>引力：月球的引力會把面向月球那一側的海水拉高，同時背向月球那一側也會因慣性隆起，這兩處就出現漲潮</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>海流</t>
+          <t>海流：黑潮帶來溫暖的海水，能調節臺灣附近的氣候使其較為溫暖，同時也帶來豐富養分形成優良漁場</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：波浪主要由風吹動海面形成，海流是大範圍海水朝固定方向的流動，潮汐則主要受月球引力牽引所造成</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>生態</t>
+          <t>生態：潮汐使潮間帶規律地時而露出、時而淹沒在海水中，這種交替的乾濕環境造就了豐富多樣的棲地與生物</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>全球：海流會把赤道附近溫暖的海水帶往高緯度地區，幫助調節全球各地的氣候冷暖，避免溫差過於極端</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>週期</t>
+          <t>週期：地球一邊自轉、月球引力一邊拉扯海水，使地球表面大致在相對的兩側同時出現海水隆起，因此一天多半會經歷兩次滿潮</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>塑形</t>
+          <t>塑形：波浪長期不斷拍打海岸，一邊侵蝕岩石形成海蝕地形，一邊把沖刷下來的沙石堆積在別處，逐漸改變海岸的樣貌</t>
         </is>
       </c>
     </row>
@@ -1830,37 +1830,37 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>波浪中海水主要如何運動？</t>
+          <t>波浪中的海水主要如何運動？</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>把低緯熱量帶往高緯調節氣候</t>
+          <t>帶來溫暖海水調節氣候並形成漁場</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>運送熱量調節氣候</t>
+          <t>原地起伏傳遞能量</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>地球自轉與月球引力共同作用</t>
+          <t>水主要原地上下起伏傳遞能量</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>原地起伏傳遞能量</t>
+          <t>隨月球引力變化</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>原地</t>
+          <t>原地：波浪傳遞時,海水質點大致只在原地做上下起伏的圓周運動,真正向前傳遞的是波浪的能量,而不是海水本身</t>
         </is>
       </c>
     </row>
@@ -1870,37 +1870,37 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>海流對全球氣候的作用？</t>
+          <t>海流對全球氣候的調節作用為何？</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>波浪風、海流定向流動、潮汐月球引力</t>
+          <t>水主要原地上下起伏傳遞能量</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>隨月球引力變化</t>
+          <t>原地起伏傳遞能量</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
+          <t>帶來溫暖海水調節氣候並形成漁場</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>運送熱量調節氣候</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>月球引力使朝月側與背側海面隆起形成漲潮</t>
-        </is>
-      </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：海流會把低緯度溫暖的海水帶往高緯度、把高緯度冷海水帶往低緯度,幫忙把熱量重新分配,調節全球各地的氣候</t>
         </is>
       </c>
     </row>
